--- a/data/trans_dic/P24D-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P24D-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha intentado dejar de fumar alguna vez</t>
+          <t>Población que ha intentado dejar de fumar alguna vez (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,92; 15,43</t>
+          <t>7,15; 15,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,37; 41,74</t>
+          <t>26,82; 42,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,55; 36,11</t>
+          <t>20,28; 36,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,68; 34,51</t>
+          <t>5,72; 31,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,41; 26,85</t>
+          <t>15,12; 26,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,72; 50,57</t>
+          <t>34,12; 49,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,59; 42,48</t>
+          <t>24,62; 42,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,64; 43,28</t>
+          <t>12,49; 43,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,93; 18,98</t>
+          <t>12,01; 18,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,39; 43,5</t>
+          <t>32,46; 43,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,01; 35,82</t>
+          <t>24,65; 35,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,52; 33,25</t>
+          <t>11,15; 31,7</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,62; 30,34</t>
+          <t>21,37; 30,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,67; 46,35</t>
+          <t>35,64; 46,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,65; 44,06</t>
+          <t>31,93; 44,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,25; 33,66</t>
+          <t>16,32; 34,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,77; 41,28</t>
+          <t>29,89; 41,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,54; 62,73</t>
+          <t>49,78; 63,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,06; 48,2</t>
+          <t>34,83; 47,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,09; 46,82</t>
+          <t>28,56; 46,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,38; 32,8</t>
+          <t>25,95; 33,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42,69; 51,47</t>
+          <t>43,54; 51,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34,52; 43,76</t>
+          <t>35,33; 43,97</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,83; 36,85</t>
+          <t>23,12; 36,45</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,3; 36,67</t>
+          <t>26,43; 37,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,09; 54,44</t>
+          <t>43,29; 54,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,93; 54,16</t>
+          <t>40,59; 53,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,68; 44,31</t>
+          <t>27,32; 44,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,29; 50,8</t>
+          <t>38,11; 50,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,35; 57,84</t>
+          <t>44,89; 57,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,1; 48,34</t>
+          <t>35,73; 47,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,89; 52,88</t>
+          <t>38,83; 53,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,15; 41,07</t>
+          <t>32,72; 41,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,58; 54,31</t>
+          <t>45,75; 54,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39,84; 49,3</t>
+          <t>40,54; 49,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35,3; 45,94</t>
+          <t>34,93; 45,47</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,21; 44,09</t>
+          <t>30,36; 44,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,0; 58,64</t>
+          <t>45,07; 58,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,13; 49,01</t>
+          <t>36,36; 48,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,34; 51,99</t>
+          <t>34,1; 52,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,23; 45,08</t>
+          <t>28,44; 44,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,13; 62,19</t>
+          <t>48,24; 62,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,27; 58,46</t>
+          <t>43,89; 57,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42,51; 54,3</t>
+          <t>42,34; 53,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,7; 41,89</t>
+          <t>31,89; 42,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49,27; 58,65</t>
+          <t>48,92; 58,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41,84; 51,05</t>
+          <t>42,21; 51,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,64; 50,29</t>
+          <t>39,96; 50,65</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,33; 59,0</t>
+          <t>41,12; 58,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,1; 63,67</t>
+          <t>47,28; 63,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47,07; 63,38</t>
+          <t>46,62; 63,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,56; 49,44</t>
+          <t>34,67; 48,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,66; 38,88</t>
+          <t>14,15; 40,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,05; 53,54</t>
+          <t>27,33; 53,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,63; 58,92</t>
+          <t>39,0; 60,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>43,61; 56,77</t>
+          <t>44,09; 57,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35,48; 51,08</t>
+          <t>35,75; 51,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43,22; 57,48</t>
+          <t>43,53; 57,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45,99; 59,42</t>
+          <t>46,53; 59,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,32; 51,06</t>
+          <t>40,19; 50,52</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,07; 62,56</t>
+          <t>36,28; 61,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34,8; 65,76</t>
+          <t>34,26; 64,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,85; 63,25</t>
+          <t>36,81; 63,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38,9; 58,14</t>
+          <t>38,99; 58,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,23; 100,0</t>
+          <t>27,81; 100,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,65; 65,6</t>
+          <t>15,39; 64,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,49; 66,27</t>
+          <t>28,73; 66,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34,75; 54,51</t>
+          <t>33,96; 55,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39,49; 64,43</t>
+          <t>39,22; 64,42</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32,46; 58,18</t>
+          <t>34,2; 59,68</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37,86; 59,77</t>
+          <t>38,23; 60,03</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39,94; 53,74</t>
+          <t>39,86; 54,27</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>36,52; 78,86</t>
+          <t>32,4; 76,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,78; 69,93</t>
+          <t>27,31; 68,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34,67; 69,75</t>
+          <t>34,31; 69,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,01; 47,91</t>
+          <t>16,09; 49,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1587,32 +1587,32 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,6; 100,0</t>
+          <t>34,81; 100,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,56; 66,79</t>
+          <t>9,3; 65,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>32,18; 70,94</t>
+          <t>31,19; 68,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27,68; 63,65</t>
+          <t>27,95; 65,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37,89; 71,54</t>
+          <t>39,35; 74,12</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,49; 47,84</t>
+          <t>20,3; 47,09</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>27,83; 32,93</t>
+          <t>28,05; 33,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>43,71; 49,11</t>
+          <t>43,54; 49,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39,76; 45,48</t>
+          <t>40,02; 45,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31,66; 39,42</t>
+          <t>31,84; 39,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,9; 38,21</t>
+          <t>31,47; 37,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,22; 54,72</t>
+          <t>47,87; 54,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,95; 47,67</t>
+          <t>41,21; 47,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>40,4; 47,24</t>
+          <t>40,08; 47,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,06; 34,34</t>
+          <t>30,02; 33,97</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45,96; 50,42</t>
+          <t>46,33; 50,75</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41,38; 45,8</t>
+          <t>41,37; 45,96</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,3; 41,83</t>
+          <t>36,2; 41,63</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha intentado dejar de fumar alguna vez</t>
+          <t>Población que ha intentado dejar de fumar alguna vez (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14249; 31794</t>
+          <t>14723; 32666</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>45197; 68935</t>
+          <t>44296; 69514</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29239; 51389</t>
+          <t>28861; 51496</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5841; 30202</t>
+          <t>5008; 27706</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26033; 45338</t>
+          <t>25533; 45106</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49363; 74019</t>
+          <t>49947; 72413</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25929; 44798</t>
+          <t>25960; 44785</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6561; 26691</t>
+          <t>7705; 26918</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44733; 71174</t>
+          <t>45048; 70774</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100908; 135521</t>
+          <t>101135; 134528</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59497; 88737</t>
+          <t>61079; 88851</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17180; 49597</t>
+          <t>16628; 47298</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86247; 121036</t>
+          <t>85251; 120260</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>124104; 161275</t>
+          <t>123988; 161306</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82628; 115037</t>
+          <t>83364; 116309</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22425; 49489</t>
+          <t>23998; 50222</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66072; 94781</t>
+          <t>68628; 95844</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>123125; 155903</t>
+          <t>123716; 156747</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74693; 102689</t>
+          <t>74202; 102118</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31948; 53252</t>
+          <t>32490; 53428</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>159563; 206166</t>
+          <t>163138; 209457</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>254597; 307015</t>
+          <t>259703; 308530</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>163664; 207478</t>
+          <t>167494; 208490</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59543; 96096</t>
+          <t>60285; 95043</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>89423; 124675</t>
+          <t>89877; 125852</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>139775; 176606</t>
+          <t>140439; 176232</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>108891; 144069</t>
+          <t>107977; 141533</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41426; 66303</t>
+          <t>40889; 65878</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>97413; 129260</t>
+          <t>96972; 128744</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>112582; 143572</t>
+          <t>111431; 143415</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77409; 106618</t>
+          <t>78804; 105153</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>52466; 71342</t>
+          <t>52389; 71636</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>197030; 244130</t>
+          <t>194484; 246827</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>260999; 310998</t>
+          <t>261967; 309460</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>193864; 239856</t>
+          <t>197260; 239961</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>100451; 130728</t>
+          <t>99392; 129385</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>72929; 103020</t>
+          <t>70939; 103264</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>128705; 164060</t>
+          <t>126099; 162504</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100368; 136160</t>
+          <t>101005; 134608</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61603; 96058</t>
+          <t>63006; 97496</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40495; 64656</t>
+          <t>40796; 63743</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>114110; 147454</t>
+          <t>114381; 147539</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>102177; 134949</t>
+          <t>101310; 133309</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>68543; 87554</t>
+          <t>68259; 86949</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>119535; 157957</t>
+          <t>120273; 158752</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>254684; 303169</t>
+          <t>252854; 301045</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212824; 259656</t>
+          <t>214687; 260641</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>137164; 174017</t>
+          <t>138246; 175241</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>52789; 75350</t>
+          <t>52520; 74690</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73655; 99567</t>
+          <t>73938; 99627</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69110; 93067</t>
+          <t>68454; 92859</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59178; 84652</t>
+          <t>59373; 83559</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6406; 18229</t>
+          <t>6633; 18880</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17833; 35291</t>
+          <t>18016; 35090</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44069; 67224</t>
+          <t>44490; 68460</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>52227; 67983</t>
+          <t>52795; 68860</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61946; 89189</t>
+          <t>62423; 89455</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>96084; 127770</t>
+          <t>96753; 128099</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>119996; 155040</t>
+          <t>121414; 155337</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>117326; 148568</t>
+          <t>116950; 146997</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19711; 33263</t>
+          <t>19292; 32665</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17837; 33702</t>
+          <t>17559; 33028</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20876; 36829</t>
+          <t>21434; 36775</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26294; 39302</t>
+          <t>26353; 39849</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1793; 6585</t>
+          <t>1832; 6585</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3164; 12467</t>
+          <t>2925; 12175</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8253; 19898</t>
+          <t>8626; 19991</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16950; 26592</t>
+          <t>16565; 26960</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23600; 38504</t>
+          <t>23440; 38497</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22805; 40877</t>
+          <t>24029; 41931</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33412; 52752</t>
+          <t>33743; 52984</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>46483; 62535</t>
+          <t>46389; 63151</t>
         </is>
       </c>
     </row>
@@ -3316,22 +3316,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7743; 16717</t>
+          <t>6869; 16272</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7785; 18917</t>
+          <t>7388; 18487</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8273; 16645</t>
+          <t>8188; 16558</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3238; 9117</t>
+          <t>3063; 9495</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3346,32 +3346,32 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1491; 8014</t>
+          <t>2790; 8014</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>601; 4204</t>
+          <t>585; 4139</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8314; 18327</t>
+          <t>8057; 17807</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8604; 19782</t>
+          <t>8687; 20497</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12077; 22806</t>
+          <t>12544; 23628</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4936; 12116</t>
+          <t>5141; 11924</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>384310; 454734</t>
+          <t>387290; 456308</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>590891; 663949</t>
+          <t>588595; 664147</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>467578; 534850</t>
+          <t>470680; 539975</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>261761; 325962</t>
+          <t>263266; 325930</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>272592; 326520</t>
+          <t>268931; 323551</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>467390; 530327</t>
+          <t>463910; 527689</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>377594; 439527</t>
+          <t>379914; 442177</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>261133; 305334</t>
+          <t>259098; 304949</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>671967; 767700</t>
+          <t>671062; 759321</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1066822; 1170387</t>
+          <t>1075336; 1178002</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>868127; 960933</t>
+          <t>868049; 964351</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>534770; 616261</t>
+          <t>533230; 613310</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P24D-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P24D-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,15; 15,85</t>
+          <t>7,3; 15,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,82; 42,09</t>
+          <t>26,91; 41,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,28; 36,19</t>
+          <t>19,81; 36,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,72; 31,66</t>
+          <t>10,53; 41,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,12; 26,71</t>
+          <t>14,58; 26,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,12; 49,47</t>
+          <t>34,19; 50,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,62; 42,47</t>
+          <t>25,4; 43,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,49; 43,65</t>
+          <t>13,79; 44,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,01; 18,88</t>
+          <t>11,98; 19,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,46; 43,18</t>
+          <t>32,87; 43,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,65; 35,86</t>
+          <t>24,52; 35,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,15; 31,7</t>
+          <t>14,67; 36,39</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,37; 30,14</t>
+          <t>21,44; 30,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,64; 46,36</t>
+          <t>35,64; 46,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,93; 44,55</t>
+          <t>31,87; 43,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,32; 34,16</t>
+          <t>16,57; 34,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,89; 41,74</t>
+          <t>28,75; 41,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,78; 63,07</t>
+          <t>49,94; 63,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,83; 47,94</t>
+          <t>35,14; 48,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,56; 46,97</t>
+          <t>27,27; 44,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,95; 33,32</t>
+          <t>25,62; 32,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43,54; 51,73</t>
+          <t>42,74; 51,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35,33; 43,97</t>
+          <t>34,53; 43,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,12; 36,45</t>
+          <t>23,01; 35,61</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>41,1%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,43; 37,01</t>
+          <t>26,38; 36,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,29; 54,33</t>
+          <t>42,93; 54,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,59; 53,2</t>
+          <t>41,83; 54,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,32; 44,02</t>
+          <t>28,76; 44,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,11; 50,6</t>
+          <t>37,72; 50,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,89; 57,77</t>
+          <t>45,48; 58,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,73; 47,68</t>
+          <t>35,85; 48,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,83; 53,09</t>
+          <t>38,79; 53,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,72; 41,52</t>
+          <t>33,02; 41,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,75; 54,04</t>
+          <t>45,66; 54,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40,54; 49,32</t>
+          <t>39,9; 49,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34,93; 45,47</t>
+          <t>35,81; 46,23</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>43,04%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,36; 44,19</t>
+          <t>30,18; 43,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,07; 58,08</t>
+          <t>46,35; 59,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,36; 48,46</t>
+          <t>36,75; 49,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,1; 52,77</t>
+          <t>31,86; 46,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,44; 44,44</t>
+          <t>28,73; 45,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,24; 62,23</t>
+          <t>48,22; 62,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,89; 57,75</t>
+          <t>44,69; 57,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42,34; 53,93</t>
+          <t>42,04; 54,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,89; 42,1</t>
+          <t>31,84; 42,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48,92; 58,24</t>
+          <t>49,13; 58,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42,21; 51,24</t>
+          <t>41,82; 51,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,96; 50,65</t>
+          <t>38,01; 47,73</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>46,3%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,12; 58,48</t>
+          <t>40,6; 58,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,28; 63,71</t>
+          <t>46,44; 63,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,62; 63,24</t>
+          <t>46,81; 63,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,67; 48,8</t>
+          <t>35,52; 49,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,15; 40,27</t>
+          <t>15,17; 41,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,33; 53,23</t>
+          <t>27,63; 53,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,0; 60,01</t>
+          <t>39,56; 59,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>44,09; 57,5</t>
+          <t>45,12; 58,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35,75; 51,23</t>
+          <t>35,88; 50,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43,53; 57,63</t>
+          <t>43,45; 57,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46,53; 59,53</t>
+          <t>46,64; 59,79</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,19; 50,52</t>
+          <t>41,63; 51,17</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>47,28%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36,28; 61,43</t>
+          <t>37,08; 61,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34,26; 64,44</t>
+          <t>33,87; 63,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36,81; 63,15</t>
+          <t>36,25; 62,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38,99; 58,95</t>
+          <t>39,69; 59,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,81; 100,0</t>
+          <t>27,23; 100,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,39; 64,07</t>
+          <t>18,37; 65,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,73; 66,58</t>
+          <t>27,21; 67,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33,96; 55,27</t>
+          <t>34,12; 54,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39,22; 64,42</t>
+          <t>39,77; 63,13</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34,2; 59,68</t>
+          <t>32,85; 58,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38,23; 60,03</t>
+          <t>37,96; 59,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39,86; 54,27</t>
+          <t>40,38; 54,52</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -1557,27 +1557,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32,4; 76,75</t>
+          <t>36,63; 77,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27,31; 68,34</t>
+          <t>29,33; 70,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34,31; 69,39</t>
+          <t>35,2; 72,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,09; 49,89</t>
+          <t>17,82; 50,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,26</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1587,32 +1587,32 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,81; 100,0</t>
+          <t>18,55; 100,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,3; 65,76</t>
+          <t>9,31; 66,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31,19; 68,93</t>
+          <t>31,02; 70,29</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27,95; 65,95</t>
+          <t>26,53; 64,72</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39,35; 74,12</t>
+          <t>37,89; 71,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,3; 47,09</t>
+          <t>18,46; 47,28</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,05; 33,05</t>
+          <t>28,03; 33,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>43,54; 49,13</t>
+          <t>43,47; 49,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40,02; 45,91</t>
+          <t>40,02; 45,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31,84; 39,42</t>
+          <t>31,92; 39,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,47; 37,87</t>
+          <t>31,4; 37,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,87; 54,45</t>
+          <t>47,64; 54,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,21; 47,96</t>
+          <t>41,41; 47,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>40,08; 47,18</t>
+          <t>40,3; 46,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,02; 33,97</t>
+          <t>30,15; 34,1</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46,33; 50,75</t>
+          <t>45,98; 50,37</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41,37; 45,96</t>
+          <t>41,47; 45,84</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,2; 41,63</t>
+          <t>36,86; 41,98</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>20851</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29857</t>
+          <t>40086</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14723; 32666</t>
+          <t>15040; 31828</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44296; 69514</t>
+          <t>44445; 68395</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28861; 51496</t>
+          <t>28191; 51433</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5008; 27706</t>
+          <t>9435; 36977</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25533; 45106</t>
+          <t>24618; 45131</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49947; 72413</t>
+          <t>50049; 74065</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25960; 44785</t>
+          <t>26786; 45660</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7705; 26918</t>
+          <t>9463; 30791</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45048; 70774</t>
+          <t>44901; 71480</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101135; 134528</t>
+          <t>102397; 135755</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61079; 88851</t>
+          <t>60744; 87806</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16628; 47298</t>
+          <t>23209; 57583</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35282</t>
+          <t>39902</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>42339</t>
+          <t>43064</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77621</t>
+          <t>82967</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>85251; 120260</t>
+          <t>85532; 121580</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>123988; 161306</t>
+          <t>123998; 161728</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83364; 116309</t>
+          <t>83214; 114013</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23998; 50222</t>
+          <t>26776; 55851</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68628; 95844</t>
+          <t>66021; 96120</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>123716; 156747</t>
+          <t>124127; 156896</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74202; 102118</t>
+          <t>74862; 102713</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32490; 53428</t>
+          <t>32973; 54394</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>163138; 209457</t>
+          <t>161051; 206913</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>259703; 308530</t>
+          <t>254934; 306029</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>167494; 208490</t>
+          <t>163724; 207062</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>60285; 95043</t>
+          <t>65006; 100607</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53292</t>
+          <t>62257</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61700</t>
+          <t>66708</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>114993</t>
+          <t>128966</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>89877; 125852</t>
+          <t>89686; 123445</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>140439; 176232</t>
+          <t>139255; 175959</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107977; 141533</t>
+          <t>111271; 143818</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40889; 65878</t>
+          <t>48421; 75234</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>96972; 128744</t>
+          <t>95975; 128297</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>111431; 143415</t>
+          <t>112908; 144306</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78804; 105153</t>
+          <t>79058; 106235</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>52389; 71636</t>
+          <t>56417; 77518</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>194484; 246827</t>
+          <t>196260; 243930</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>261967; 309460</t>
+          <t>261437; 310738</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>197260; 239961</t>
+          <t>194122; 240618</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>99392; 129385</t>
+          <t>112358; 145072</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77668</t>
+          <t>75557</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>77849</t>
+          <t>82673</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>155517</t>
+          <t>158230</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>70939; 103264</t>
+          <t>70524; 102082</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>126099; 162504</t>
+          <t>129671; 165374</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>101005; 134608</t>
+          <t>102078; 137085</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63006; 97496</t>
+          <t>62225; 90189</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40796; 63743</t>
+          <t>41204; 64671</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>114381; 147539</t>
+          <t>114328; 147842</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>101310; 133309</t>
+          <t>103166; 132931</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>68259; 86949</t>
+          <t>72444; 93096</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>120273; 158752</t>
+          <t>120075; 159057</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>252854; 301045</t>
+          <t>253966; 302928</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>214687; 260641</t>
+          <t>212732; 260137</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>138246; 175241</t>
+          <t>139735; 175479</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71863</t>
+          <t>78328</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>60517</t>
+          <t>68736</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>132381</t>
+          <t>147065</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>52520; 74690</t>
+          <t>51850; 74289</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73938; 99627</t>
+          <t>72619; 98514</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>68454; 92859</t>
+          <t>68736; 92854</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59373; 83559</t>
+          <t>65810; 91501</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6633; 18880</t>
+          <t>7114; 19250</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18016; 35090</t>
+          <t>18212; 35541</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44490; 68460</t>
+          <t>45137; 68123</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>52795; 68860</t>
+          <t>59700; 78031</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>62423; 89455</t>
+          <t>62642; 88615</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>96753; 128099</t>
+          <t>96583; 128190</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>121414; 155337</t>
+          <t>121699; 156005</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>116950; 146997</t>
+          <t>132233; 162514</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>36567</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>21627</t>
+          <t>24216</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>54552</t>
+          <t>60782</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19292; 32665</t>
+          <t>19716; 32803</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17559; 33028</t>
+          <t>17360; 32409</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21434; 36775</t>
+          <t>21109; 36241</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26353; 39849</t>
+          <t>29367; 43933</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1832; 6585</t>
+          <t>1793; 6585</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2925; 12175</t>
+          <t>3490; 12369</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8626; 19991</t>
+          <t>8170; 20173</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16565; 26960</t>
+          <t>18615; 29685</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23440; 38497</t>
+          <t>23764; 37725</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24029; 41931</t>
+          <t>23081; 41132</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33743; 52984</t>
+          <t>33504; 52284</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>46389; 63151</t>
+          <t>51910; 70089</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8768</t>
         </is>
       </c>
     </row>
@@ -3316,27 +3316,27 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6869; 16272</t>
+          <t>7765; 16426</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7388; 18487</t>
+          <t>7935; 19202</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8188; 16558</t>
+          <t>8399; 17279</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3063; 9495</t>
+          <t>3598; 10286</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3442</t>
+          <t>0; 4635</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3346,32 +3346,32 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2790; 8014</t>
+          <t>1486; 8014</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>585; 4139</t>
+          <t>631; 4478</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8057; 17807</t>
+          <t>8014; 18160</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8687; 20497</t>
+          <t>8246; 20116</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12544; 23628</t>
+          <t>12079; 22863</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5141; 11924</t>
+          <t>4979; 12751</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>291294</t>
+          <t>319831</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>281709</t>
+          <t>307031</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>573003</t>
+          <t>626863</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>387290; 456308</t>
+          <t>387022; 457836</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>588595; 664147</t>
+          <t>587726; 662984</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>470680; 539975</t>
+          <t>470649; 540294</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>263266; 325930</t>
+          <t>285482; 353950</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>268931; 323551</t>
+          <t>268296; 324646</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>463910; 527689</t>
+          <t>461690; 528034</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>379914; 442177</t>
+          <t>381797; 441009</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>259098; 304949</t>
+          <t>282477; 329045</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>671062; 759321</t>
+          <t>673899; 762196</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1075336; 1178002</t>
+          <t>1067264; 1169235</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>868049; 964351</t>
+          <t>870043; 961813</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>533230; 613310</t>
+          <t>588102; 669762</t>
         </is>
       </c>
     </row>
